--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -29,10 +29,10 @@
     <t>EndJump</t>
   </si>
   <si>
-    <t>101_output</t>
-  </si>
-  <si>
-    <t>オープニング</t>
+    <t>Interrude1-1</t>
+  </si>
+  <si>
+    <t>Interrude1-2</t>
   </si>
   <si>
     <t>なし</t>
@@ -82,10 +82,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -96,16 +96,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -119,22 +147,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -142,46 +164,48 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -193,48 +217,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,181 +255,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -445,29 +445,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -502,11 +482,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -526,17 +521,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -548,145 +548,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1013,8 +1013,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="20.4545454545455" customWidth="1"/>
@@ -1034,7 +1034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1051,8 +1051,23 @@
         <f>INDEX(Define!B:B,MATCH(D2,Define!A:A))</f>
         <v>戦略</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3" t="str">
+        <f>INDEX(Define!B:B,MATCH(D3,Define!A:A))</f>
+        <v>戦略</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -33,6 +33,9 @@
   </si>
   <si>
     <t>Interrude1-2</t>
+  </si>
+  <si>
+    <t>Dungeon30-1</t>
   </si>
   <si>
     <t>なし</t>
@@ -82,10 +85,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -97,61 +100,138 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -162,83 +242,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -249,25 +252,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,13 +402,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,139 +432,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,8 +449,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -467,17 +470,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -500,23 +514,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -529,17 +543,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -548,145 +551,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1013,8 +1016,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="20.4545454545455" customWidth="1"/>
@@ -1068,6 +1071,20 @@
       <c r="E3" t="str">
         <f>INDEX(Define!B:B,MATCH(D3,Define!A:A))</f>
         <v>戦略</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>1030</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1092,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1100,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1108,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1116,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1124,7 +1141,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1132,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1140,7 +1157,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1148,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1156,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1164,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1172,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1180,7 +1197,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1188,7 +1205,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1196,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Id</t>
   </si>
@@ -35,7 +35,13 @@
     <t>Interrude1-2</t>
   </si>
   <si>
+    <t>Encount</t>
+  </si>
+  <si>
     <t>Dungeon30-1</t>
+  </si>
+  <si>
+    <t>Dungeon40-1</t>
   </si>
   <si>
     <t>なし</t>
@@ -99,6 +105,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -107,90 +143,61 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -204,34 +211,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,169 +258,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -443,15 +449,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -472,26 +469,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -513,9 +493,44 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,15 +549,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -551,7 +557,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,7 +566,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -569,127 +575,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1016,8 +1022,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="20.4545454545455" customWidth="1"/>
@@ -1073,9 +1079,9 @@
         <v>戦略</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" customFormat="1" spans="1:4">
       <c r="A4">
-        <v>1030</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -1084,6 +1090,34 @@
         <v>0</v>
       </c>
       <c r="D4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>1030</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:4">
+      <c r="A6">
+        <v>1040</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>9</v>
       </c>
     </row>
@@ -1109,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1117,7 +1151,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1125,7 +1159,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1133,7 +1167,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1141,7 +1175,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1149,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1157,7 +1191,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1165,7 +1199,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1173,7 +1207,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1181,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1189,7 +1223,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1197,7 +1231,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1205,7 +1239,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1213,7 +1247,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <t>Encount</t>
+  </si>
+  <si>
+    <t>Curse</t>
+  </si>
+  <si>
+    <t>Curse2</t>
   </si>
   <si>
     <t>Dungeon30-1</t>
@@ -91,9 +97,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -106,89 +112,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -197,7 +120,75 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,6 +204,44 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -220,32 +249,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -258,19 +264,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,19 +408,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,139 +438,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,6 +455,56 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -476,50 +532,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -535,17 +547,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -557,7 +563,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -566,7 +572,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -575,127 +581,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1022,8 +1028,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="20.4545454545455" customWidth="1"/>
@@ -1093,9 +1099,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" customFormat="1" spans="1:4">
       <c r="A5">
-        <v>1030</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -1109,7 +1115,7 @@
     </row>
     <row r="6" customFormat="1" spans="1:4">
       <c r="A6">
-        <v>1040</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -1118,6 +1124,34 @@
         <v>0</v>
       </c>
       <c r="D6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>1030</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:4">
+      <c r="A8">
+        <v>1040</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>9</v>
       </c>
     </row>
@@ -1143,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1151,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1159,7 +1193,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1167,7 +1201,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1175,7 +1209,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1183,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1191,7 +1225,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1199,7 +1233,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1207,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1215,7 +1249,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1223,7 +1257,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1231,7 +1265,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1239,7 +1273,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1247,7 +1281,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Curse2</t>
+  </si>
+  <si>
+    <t>EndCurse</t>
   </si>
   <si>
     <t>Dungeon30-1</t>
@@ -97,10 +100,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -108,6 +111,51 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,14 +175,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,23 +205,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,8 +219,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -181,75 +253,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,19 +267,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -288,36 +387,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -330,121 +435,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,43 +470,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -519,6 +490,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,9 +535,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,145 +566,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1028,8 +1031,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="20.4545454545455" customWidth="1"/>
@@ -1127,9 +1130,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" customFormat="1" spans="1:4">
       <c r="A7">
-        <v>1030</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1141,9 +1144,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:4">
+    <row r="8" spans="1:4">
       <c r="A8">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1152,6 +1155,20 @@
         <v>0</v>
       </c>
       <c r="D8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:4">
+      <c r="A9">
+        <v>1040</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>9</v>
       </c>
     </row>
@@ -1177,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1185,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1193,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1201,7 +1218,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1209,7 +1226,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1217,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1225,7 +1242,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1233,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1241,7 +1258,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1249,7 +1266,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1257,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1265,7 +1282,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1273,7 +1290,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1281,7 +1298,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>EndCurse</t>
+  </si>
+  <si>
+    <t>Magic</t>
   </si>
   <si>
     <t>Dungeon30-1</t>
@@ -100,10 +103,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -114,6 +117,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -122,7 +126,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,6 +171,37 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -143,14 +215,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -167,30 +231,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -203,9 +246,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,45 +260,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -267,55 +270,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,127 +438,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,8 +466,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -480,6 +485,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -490,6 +510,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,47 +561,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -566,145 +569,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1031,7 +1034,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1144,9 +1147,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" customFormat="1" spans="1:4">
       <c r="A8">
-        <v>1030</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1158,9 +1161,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:4">
+    <row r="9" spans="1:4">
       <c r="A9">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1169,6 +1172,20 @@
         <v>0</v>
       </c>
       <c r="D9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:4">
+      <c r="A10">
+        <v>1040</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>9</v>
       </c>
     </row>
@@ -1194,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1202,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1210,7 +1227,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1218,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1226,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1234,7 +1251,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1242,7 +1259,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1250,7 +1267,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1258,7 +1275,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1266,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1274,7 +1291,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1282,7 +1299,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1290,7 +1307,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1298,7 +1315,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Dungeon40-1</t>
+  </si>
+  <si>
+    <t>Dungeon42-1</t>
   </si>
   <si>
     <t>なし</t>
@@ -103,10 +106,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -117,23 +120,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,66 +155,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -215,9 +166,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,33 +248,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -270,25 +273,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,157 +381,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,22 +467,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,6 +512,33 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -531,33 +556,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,145 +572,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1034,7 +1037,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1186,6 +1189,20 @@
         <v>0</v>
       </c>
       <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:4">
+      <c r="A11">
+        <v>1050</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>9</v>
       </c>
     </row>
@@ -1211,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1219,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1227,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1235,7 +1252,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1243,7 +1260,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1251,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1259,7 +1276,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1267,7 +1284,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1275,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1283,7 +1300,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1291,7 +1308,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1299,7 +1316,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1307,7 +1324,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1315,7 +1332,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t>Interrude1-2</t>
+  </si>
+  <si>
+    <t>Interrude2-1</t>
+  </si>
+  <si>
+    <t>Interrude2-2</t>
   </si>
   <si>
     <t>Encount</t>
@@ -106,10 +112,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -120,6 +126,80 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -129,32 +209,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -167,74 +240,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,9 +255,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,13 +279,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,43 +411,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,115 +447,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,32 +473,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -508,6 +508,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -530,25 +545,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -572,16 +578,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -593,124 +599,124 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1037,7 +1043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1094,9 +1100,9 @@
         <v>戦略</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:4">
+    <row r="4" customFormat="1" spans="1:5">
       <c r="A4">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -1107,10 +1113,14 @@
       <c r="D4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:4">
+      <c r="E4" t="str">
+        <f>INDEX(Define!B:B,MATCH(D4,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:5">
       <c r="A5">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -1121,10 +1131,14 @@
       <c r="D5">
         <v>9</v>
       </c>
+      <c r="E5" t="str">
+        <f>INDEX(Define!B:B,MATCH(D5,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
     </row>
     <row r="6" customFormat="1" spans="1:4">
       <c r="A6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -1138,7 +1152,7 @@
     </row>
     <row r="7" customFormat="1" spans="1:4">
       <c r="A7">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1152,7 +1166,7 @@
     </row>
     <row r="8" customFormat="1" spans="1:4">
       <c r="A8">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1164,9 +1178,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" customFormat="1" spans="1:4">
       <c r="A9">
-        <v>1030</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1180,7 +1194,7 @@
     </row>
     <row r="10" customFormat="1" spans="1:4">
       <c r="A10">
-        <v>1040</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1192,9 +1206,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:4">
+    <row r="11" spans="1:4">
       <c r="A11">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1203,6 +1217,34 @@
         <v>0</v>
       </c>
       <c r="D11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:4">
+      <c r="A12">
+        <v>1040</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:4">
+      <c r="A13">
+        <v>1050</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>9</v>
       </c>
     </row>
@@ -1228,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1236,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1244,7 +1286,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1252,7 +1294,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1260,7 +1302,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1268,7 +1310,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1276,7 +1318,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1284,7 +1326,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1292,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1300,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1308,7 +1350,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1316,7 +1358,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1324,7 +1366,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1332,7 +1374,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Id</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Dungeon42-1</t>
+  </si>
+  <si>
+    <t>Dungeon52-1</t>
   </si>
   <si>
     <t>なし</t>
@@ -112,9 +115,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -126,6 +129,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -134,82 +168,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,9 +184,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,32 +252,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,13 +282,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,169 +450,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,74 +476,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -562,6 +502,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -570,6 +519,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -578,145 +581,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1043,7 +1046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1245,6 +1248,20 @@
         <v>0</v>
       </c>
       <c r="D13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:4">
+      <c r="A14">
+        <v>1060</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>9</v>
       </c>
     </row>
@@ -1270,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1278,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1286,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1294,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1302,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1310,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1318,7 +1335,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1326,7 +1343,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1334,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1342,7 +1359,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1350,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1358,7 +1375,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1366,7 +1383,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1374,7 +1391,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Dungeon52-1</t>
+  </si>
+  <si>
+    <t>Actor0001_1</t>
   </si>
   <si>
     <t>なし</t>
@@ -115,9 +118,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -130,13 +133,34 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -145,6 +169,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -153,6 +193,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -160,19 +237,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,90 +261,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,13 +285,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,169 +429,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -480,7 +483,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -496,6 +514,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -519,60 +576,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -581,145 +584,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1046,7 +1049,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1262,6 +1265,20 @@
         <v>0</v>
       </c>
       <c r="D14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>10010</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>9</v>
       </c>
     </row>
@@ -1287,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1295,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1303,7 +1320,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1311,7 +1328,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1319,7 +1336,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1327,7 +1344,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1335,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1343,7 +1360,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1351,7 +1368,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1359,7 +1376,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1367,7 +1384,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1375,7 +1392,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1383,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1391,7 +1408,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Id</t>
   </si>
@@ -39,6 +39,12 @@
   </si>
   <si>
     <t>Interrude2-2</t>
+  </si>
+  <si>
+    <t>Interrude3-1</t>
+  </si>
+  <si>
+    <t>Interrude3-2</t>
   </si>
   <si>
     <t>Encount</t>
@@ -118,9 +124,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -132,6 +138,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -140,13 +183,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -155,91 +230,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,29 +281,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -285,19 +291,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,7 +393,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,151 +423,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,11 +485,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -503,21 +515,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -533,17 +530,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -559,15 +550,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -576,6 +558,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -584,145 +590,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1049,7 +1055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1142,9 +1148,9 @@
         <v>戦略</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:4">
+    <row r="6" customFormat="1" spans="1:5">
       <c r="A6">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -1155,10 +1161,14 @@
       <c r="D6">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:4">
+      <c r="E6" t="str">
+        <f>INDEX(Define!B:B,MATCH(D6,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:5">
       <c r="A7">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1168,11 +1178,15 @@
       </c>
       <c r="D7">
         <v>9</v>
+      </c>
+      <c r="E7" t="str">
+        <f>INDEX(Define!B:B,MATCH(D7,Define!A:A))</f>
+        <v>戦略</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:4">
       <c r="A8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1186,7 +1200,7 @@
     </row>
     <row r="9" customFormat="1" spans="1:4">
       <c r="A9">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1200,7 +1214,7 @@
     </row>
     <row r="10" customFormat="1" spans="1:4">
       <c r="A10">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1212,9 +1226,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" customFormat="1" spans="1:4">
       <c r="A11">
-        <v>1030</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1228,7 +1242,7 @@
     </row>
     <row r="12" customFormat="1" spans="1:4">
       <c r="A12">
-        <v>1040</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1240,9 +1254,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:4">
+    <row r="13" spans="1:4">
       <c r="A13">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1256,7 +1270,7 @@
     </row>
     <row r="14" customFormat="1" spans="1:4">
       <c r="A14">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
@@ -1268,9 +1282,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" customFormat="1" spans="1:4">
       <c r="A15">
-        <v>10010</v>
+        <v>1050</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1279,6 +1293,34 @@
         <v>0</v>
       </c>
       <c r="D15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:4">
+      <c r="A16">
+        <v>1060</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>10010</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>9</v>
       </c>
     </row>
@@ -1304,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1312,7 +1354,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1320,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1328,7 +1370,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1336,7 +1378,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1344,7 +1386,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1352,7 +1394,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1360,7 +1402,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1368,7 +1410,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1376,7 +1418,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1384,7 +1426,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1392,7 +1434,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1400,7 +1442,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1408,7 +1450,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Id</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Magic</t>
+  </si>
+  <si>
+    <t>BeforeBoss</t>
   </si>
   <si>
     <t>Dungeon30-1</t>
@@ -124,8 +127,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -138,6 +141,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -147,6 +180,52 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -160,120 +239,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -281,6 +246,44 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -291,187 +294,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,6 +485,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -500,50 +518,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -582,6 +561,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -590,7 +593,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -599,7 +602,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -608,127 +611,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1055,7 +1058,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1254,9 +1257,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" customFormat="1" spans="1:4">
       <c r="A13">
-        <v>1030</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1268,9 +1271,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:4">
+    <row r="14" spans="1:4">
       <c r="A14">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
@@ -1284,7 +1287,7 @@
     </row>
     <row r="15" customFormat="1" spans="1:4">
       <c r="A15">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1298,7 +1301,7 @@
     </row>
     <row r="16" customFormat="1" spans="1:4">
       <c r="A16">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
@@ -1310,9 +1313,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" customFormat="1" spans="1:4">
       <c r="A17">
-        <v>10010</v>
+        <v>1060</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -1321,6 +1324,20 @@
         <v>0</v>
       </c>
       <c r="D17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>10010</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>9</v>
       </c>
     </row>
@@ -1346,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1354,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1362,7 +1379,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1370,7 +1387,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1378,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1386,7 +1403,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1394,7 +1411,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1402,7 +1419,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1410,7 +1427,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1418,7 +1435,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1426,7 +1443,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1434,7 +1451,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1442,7 +1459,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1450,7 +1467,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>Id</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>Interrude3-2</t>
+  </si>
+  <si>
+    <t>Interrude4-1</t>
+  </si>
+  <si>
+    <t>Interrude4-2</t>
   </si>
   <si>
     <t>Encount</t>
@@ -127,10 +133,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -141,45 +147,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,22 +185,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,14 +223,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,6 +245,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -257,29 +270,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,43 +300,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -342,139 +468,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,21 +491,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -527,6 +518,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -534,6 +540,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -576,15 +591,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -593,145 +599,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1058,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1187,9 +1193,9 @@
         <v>戦略</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:4">
+    <row r="8" customFormat="1" spans="1:5">
       <c r="A8">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1200,10 +1206,14 @@
       <c r="D8">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:4">
+      <c r="E8" t="str">
+        <f>INDEX(Define!B:B,MATCH(D8,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:5">
       <c r="A9">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1214,10 +1224,14 @@
       <c r="D9">
         <v>9</v>
       </c>
+      <c r="E9" t="str">
+        <f>INDEX(Define!B:B,MATCH(D9,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
     </row>
     <row r="10" customFormat="1" spans="1:4">
       <c r="A10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1231,7 +1245,7 @@
     </row>
     <row r="11" customFormat="1" spans="1:4">
       <c r="A11">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1245,7 +1259,7 @@
     </row>
     <row r="12" customFormat="1" spans="1:4">
       <c r="A12">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1259,7 +1273,7 @@
     </row>
     <row r="13" customFormat="1" spans="1:4">
       <c r="A13">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1271,9 +1285,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" customFormat="1" spans="1:4">
       <c r="A14">
-        <v>1030</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
@@ -1287,7 +1301,7 @@
     </row>
     <row r="15" customFormat="1" spans="1:4">
       <c r="A15">
-        <v>1040</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1299,9 +1313,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:4">
+    <row r="16" spans="1:4">
       <c r="A16">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
@@ -1315,7 +1329,7 @@
     </row>
     <row r="17" customFormat="1" spans="1:4">
       <c r="A17">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -1327,9 +1341,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" customFormat="1" spans="1:4">
       <c r="A18">
-        <v>10010</v>
+        <v>1050</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -1338,6 +1352,34 @@
         <v>0</v>
       </c>
       <c r="D18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:4">
+      <c r="A19">
+        <v>1060</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>10010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
         <v>9</v>
       </c>
     </row>
@@ -1363,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1371,7 +1413,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1379,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1387,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1395,7 +1437,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1403,7 +1445,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1411,7 +1453,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1419,7 +1461,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1427,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1435,7 +1477,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1443,7 +1485,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1451,7 +1493,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1459,7 +1501,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1467,7 +1509,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Actor0001_1</t>
+  </si>
+  <si>
+    <t>Interrude0-1</t>
   </si>
   <si>
     <t>なし</t>
@@ -133,10 +136,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -147,31 +150,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,54 +198,61 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -245,47 +264,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,55 +303,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -360,114 +471,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -475,12 +484,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,6 +494,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -509,11 +521,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -535,20 +553,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,17 +584,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -599,145 +602,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1064,7 +1067,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1380,6 +1383,20 @@
         <v>0</v>
       </c>
       <c r="D20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>20010</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
         <v>9</v>
       </c>
     </row>
@@ -1405,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1413,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1421,7 +1438,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1429,7 +1446,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1437,7 +1454,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1445,7 +1462,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1453,7 +1470,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1461,7 +1478,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1469,7 +1486,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1477,7 +1494,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1485,7 +1502,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1493,7 +1510,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1501,7 +1518,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1509,7 +1526,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>Id</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Interrude0-1</t>
+  </si>
+  <si>
+    <t>Interrude0-2</t>
   </si>
   <si>
     <t>なし</t>
@@ -150,8 +153,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -159,7 +221,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -174,18 +236,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -197,98 +251,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,13 +306,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,25 +432,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -351,7 +450,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,127 +480,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,45 +497,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -551,20 +515,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -586,6 +547,48 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -602,7 +605,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -611,7 +614,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -620,127 +623,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1067,7 +1070,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1397,6 +1400,20 @@
         <v>0</v>
       </c>
       <c r="D21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:4">
+      <c r="A22">
+        <v>20020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
         <v>9</v>
       </c>
     </row>
@@ -1422,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1430,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1438,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1446,7 +1463,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1454,7 +1471,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1462,7 +1479,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1470,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1478,7 +1495,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1486,7 +1503,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1494,7 +1511,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1502,7 +1519,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1510,7 +1527,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1518,7 +1535,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1526,7 +1543,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="Advs" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Id</t>
   </si>
@@ -90,6 +90,21 @@
   </si>
   <si>
     <t>Interrude0-2</t>
+  </si>
+  <si>
+    <t>Opening1-1</t>
+  </si>
+  <si>
+    <t>Opening1-2</t>
+  </si>
+  <si>
+    <t>Opening1-3</t>
+  </si>
+  <si>
+    <t>Opening1-4</t>
+  </si>
+  <si>
+    <t>Opening1-5</t>
   </si>
   <si>
     <t>なし</t>
@@ -139,10 +154,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -154,7 +169,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,9 +183,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -182,6 +227,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -190,6 +258,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -197,10 +273,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -212,90 +305,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -306,187 +321,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -497,6 +512,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -530,34 +563,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -587,13 +598,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,145 +620,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1070,7 +1085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
@@ -1414,6 +1429,76 @@
         <v>0</v>
       </c>
       <c r="D22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>30010</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>30011</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>30012</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>30013</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>30014</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
         <v>9</v>
       </c>
     </row>
@@ -1439,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1447,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1455,7 +1540,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1463,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1471,7 +1556,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1479,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1487,7 +1572,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1495,7 +1580,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1503,7 +1588,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1511,7 +1596,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1519,7 +1604,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1527,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1535,7 +1620,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1543,7 +1628,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Id</t>
   </si>
@@ -26,85 +26,106 @@
     <t>PrizeSetId</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
+    <t>ReadFlag</t>
+  </si>
+  <si>
+    <t>Interrude1-1</t>
+  </si>
+  <si>
+    <t>Interrude1-2</t>
+  </si>
+  <si>
+    <t>Interrude2-1</t>
+  </si>
+  <si>
+    <t>Interrude2-2</t>
+  </si>
+  <si>
+    <t>Interrude3-1</t>
+  </si>
+  <si>
+    <t>Interrude3-2</t>
+  </si>
+  <si>
+    <t>Interrude4-1</t>
+  </si>
+  <si>
+    <t>Interrude4-2</t>
+  </si>
+  <si>
+    <t>Encount</t>
+  </si>
+  <si>
+    <t>Curse</t>
+  </si>
+  <si>
+    <t>Curse2</t>
+  </si>
+  <si>
+    <t>EndCurse</t>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>BeforeBoss</t>
+  </si>
+  <si>
+    <t>Dungeon30-1</t>
+  </si>
+  <si>
+    <t>Dungeon40-1</t>
+  </si>
+  <si>
+    <t>Dungeon42-1</t>
+  </si>
+  <si>
+    <t>Dungeon52-1</t>
+  </si>
+  <si>
+    <t>Actor0001_1</t>
+  </si>
+  <si>
+    <t>Interrude0-1</t>
+  </si>
+  <si>
+    <t>Interrude0-2</t>
+  </si>
+  <si>
+    <t>Opening1-1</t>
+  </si>
+  <si>
+    <t>Opening1-2</t>
+  </si>
+  <si>
+    <t>Opening1-3</t>
+  </si>
+  <si>
+    <t>Opening1-4</t>
+  </si>
+  <si>
+    <t>Opening1-5</t>
+  </si>
+  <si>
+    <t>Opening1-6</t>
+  </si>
+  <si>
+    <t>Opening2-1</t>
+  </si>
+  <si>
     <t>EndJump</t>
-  </si>
-  <si>
-    <t>Interrude1-1</t>
-  </si>
-  <si>
-    <t>Interrude1-2</t>
-  </si>
-  <si>
-    <t>Interrude2-1</t>
-  </si>
-  <si>
-    <t>Interrude2-2</t>
-  </si>
-  <si>
-    <t>Interrude3-1</t>
-  </si>
-  <si>
-    <t>Interrude3-2</t>
-  </si>
-  <si>
-    <t>Interrude4-1</t>
-  </si>
-  <si>
-    <t>Interrude4-2</t>
-  </si>
-  <si>
-    <t>Encount</t>
-  </si>
-  <si>
-    <t>Curse</t>
-  </si>
-  <si>
-    <t>Curse2</t>
-  </si>
-  <si>
-    <t>EndCurse</t>
-  </si>
-  <si>
-    <t>Magic</t>
-  </si>
-  <si>
-    <t>BeforeBoss</t>
-  </si>
-  <si>
-    <t>Dungeon30-1</t>
-  </si>
-  <si>
-    <t>Dungeon40-1</t>
-  </si>
-  <si>
-    <t>Dungeon42-1</t>
-  </si>
-  <si>
-    <t>Dungeon52-1</t>
-  </si>
-  <si>
-    <t>Actor0001_1</t>
-  </si>
-  <si>
-    <t>Interrude0-1</t>
-  </si>
-  <si>
-    <t>Interrude0-2</t>
-  </si>
-  <si>
-    <t>Opening1-1</t>
-  </si>
-  <si>
-    <t>Opening1-2</t>
-  </si>
-  <si>
-    <t>Opening1-3</t>
-  </si>
-  <si>
-    <t>Opening1-4</t>
-  </si>
-  <si>
-    <t>Opening1-5</t>
   </si>
   <si>
     <t>なし</t>
@@ -169,7 +190,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,14 +220,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,7 +266,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,9 +280,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,75 +332,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -321,175 +342,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,11 +536,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -529,21 +582,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -565,11 +603,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,38 +628,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,7 +641,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -629,136 +650,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1085,14 +1106,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="3" width="13.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="20.4545454545455" customWidth="1"/>
+    <col min="2" max="7" width="13.2727272727273" customWidth="1"/>
+    <col min="10" max="10" width="20.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1105,401 +1126,745 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2" t="str">
-        <f>INDEX(Define!B:B,MATCH(D2,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3" t="str">
-        <f>INDEX(Define!B:B,MATCH(D3,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:8">
       <c r="A4">
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4" t="str">
-        <f>INDEX(Define!B:B,MATCH(D4,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:8">
       <c r="A5">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5" t="str">
-        <f>INDEX(Define!B:B,MATCH(D5,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:8">
       <c r="A6">
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" t="str">
-        <f>INDEX(Define!B:B,MATCH(D6,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:8">
       <c r="A7">
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7" t="str">
-        <f>INDEX(Define!B:B,MATCH(D7,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:8">
       <c r="A8">
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8" t="str">
-        <f>INDEX(Define!B:B,MATCH(D8,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:8">
       <c r="A9">
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9" t="str">
-        <f>INDEX(Define!B:B,MATCH(D9,Define!A:A))</f>
-        <v>戦略</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:8">
       <c r="A10">
         <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:8">
       <c r="A11">
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:8">
       <c r="A12">
         <v>120</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:8">
       <c r="A13">
         <v>130</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:8">
       <c r="A14">
         <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:8">
       <c r="A15">
         <v>150</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>1030</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:8">
       <c r="A17">
         <v>1040</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:8">
       <c r="A18">
         <v>1050</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:8">
       <c r="A19">
         <v>1060</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>10010</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20010</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:8">
       <c r="A22">
         <v>20020</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>30010</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>30011</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>30012</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>30013</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>30014</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>30015</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>30110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>2010</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1516,7 +1881,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1524,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1532,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1540,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1548,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1556,7 +1921,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1564,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1572,7 +1937,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1580,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1588,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1596,7 +1961,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1604,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1612,7 +1977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1620,7 +1985,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1628,7 +1993,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -175,9 +175,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -190,9 +190,61 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -213,22 +265,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,23 +279,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -274,9 +312,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -288,50 +326,12 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -342,19 +342,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -366,127 +510,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,30 +523,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,80 +533,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -633,6 +559,80 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -641,7 +641,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -650,136 +650,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Opening1-1</t>
+  </si>
+  <si>
+    <t>Opening1-1b</t>
   </si>
   <si>
     <t>Opening1-2</t>
@@ -175,8 +178,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -190,28 +193,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,9 +229,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,17 +268,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,6 +282,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -280,10 +306,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -297,9 +323,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -309,29 +335,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -342,37 +345,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,145 +477,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,6 +536,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -547,15 +574,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -575,25 +593,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -622,17 +636,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -641,7 +644,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -650,7 +653,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -659,127 +662,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1106,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="7" width="13.2727272727273" customWidth="1"/>
@@ -1696,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1711,7 +1714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
         <v>30011</v>
       </c>
@@ -1739,7 +1742,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>30012</v>
+        <v>30020</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1765,7 +1768,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>30013</v>
+        <v>30030</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -1791,7 +1794,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>30014</v>
+        <v>30040</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -1817,7 +1820,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>30015</v>
+        <v>30050</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -1843,7 +1846,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>30110</v>
+        <v>30060</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -1852,18 +1855,44 @@
         <v>0</v>
       </c>
       <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>30110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
         <v>2010</v>
       </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29" t="b">
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1881,7 +1910,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1889,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1897,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1905,7 +1934,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1913,7 +1942,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1921,7 +1950,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1929,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1937,7 +1966,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1945,7 +1974,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1953,7 +1982,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1961,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1969,7 +1998,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1977,7 +2006,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1985,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1993,7 +2022,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -96,6 +96,93 @@
   </si>
   <si>
     <t>Actor0001_1</t>
+  </si>
+  <si>
+    <t>Actor0001_2</t>
+  </si>
+  <si>
+    <t>Actor0001_3</t>
+  </si>
+  <si>
+    <t>Actor0002_1</t>
+  </si>
+  <si>
+    <t>Actor0002_2</t>
+  </si>
+  <si>
+    <t>Actor0002_3</t>
+  </si>
+  <si>
+    <t>Actor0003_1</t>
+  </si>
+  <si>
+    <t>Actor0003_2</t>
+  </si>
+  <si>
+    <t>Actor0003_3</t>
+  </si>
+  <si>
+    <t>Actor0004_1</t>
+  </si>
+  <si>
+    <t>Actor0004_2</t>
+  </si>
+  <si>
+    <t>Actor0004_3</t>
+  </si>
+  <si>
+    <t>Actor0005_1</t>
+  </si>
+  <si>
+    <t>Actor0005_2</t>
+  </si>
+  <si>
+    <t>Actor0005_3</t>
+  </si>
+  <si>
+    <t>Actor0006_1</t>
+  </si>
+  <si>
+    <t>Actor0006_2</t>
+  </si>
+  <si>
+    <t>Actor0006_3</t>
+  </si>
+  <si>
+    <t>Actor0007_1</t>
+  </si>
+  <si>
+    <t>Actor0007_2</t>
+  </si>
+  <si>
+    <t>Actor0007_3</t>
+  </si>
+  <si>
+    <t>Actor0008_1</t>
+  </si>
+  <si>
+    <t>Actor0008_2</t>
+  </si>
+  <si>
+    <t>Actor0008_3</t>
+  </si>
+  <si>
+    <t>Actor0009_1</t>
+  </si>
+  <si>
+    <t>Actor0009_2</t>
+  </si>
+  <si>
+    <t>Actor0009_3</t>
+  </si>
+  <si>
+    <t>Actor0010_1</t>
+  </si>
+  <si>
+    <t>Actor0010_2</t>
+  </si>
+  <si>
+    <t>Actor0010_3</t>
   </si>
   <si>
     <t>Interrude0-1</t>
@@ -178,9 +265,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -192,8 +279,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -207,16 +295,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,24 +355,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,8 +371,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,25 +393,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,20 +408,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -345,31 +432,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,37 +600,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,109 +612,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -549,6 +636,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -563,17 +665,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,6 +706,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -612,30 +723,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -644,16 +731,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,127 +749,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1109,7 +1196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="7" width="13.2727272727273" customWidth="1"/>
@@ -1612,7 +1699,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>10010</v>
+        <v>10110</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
@@ -1636,9 +1723,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" customFormat="1" spans="1:8">
       <c r="A21">
-        <v>20010</v>
+        <v>10120</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -1664,7 +1751,7 @@
     </row>
     <row r="22" customFormat="1" spans="1:8">
       <c r="A22">
-        <v>20020</v>
+        <v>10130</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
@@ -1688,9 +1775,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" customFormat="1" spans="1:8">
       <c r="A23">
-        <v>30010</v>
+        <v>10210</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
@@ -1699,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1716,7 +1803,7 @@
     </row>
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
-        <v>30011</v>
+        <v>10220</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -1740,9 +1827,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" customFormat="1" spans="1:8">
       <c r="A25">
-        <v>30020</v>
+        <v>10230</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1766,9 +1853,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
-        <v>30030</v>
+        <v>10310</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -1792,9 +1879,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" customFormat="1" spans="1:8">
       <c r="A27">
-        <v>30040</v>
+        <v>10320</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -1818,9 +1905,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
-        <v>30050</v>
+        <v>10330</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -1844,9 +1931,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>30060</v>
+        <v>10410</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -1870,9 +1957,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
-        <v>30110</v>
+        <v>10420</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
@@ -1881,18 +1968,772 @@
         <v>0</v>
       </c>
       <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:8">
+      <c r="A31">
+        <v>10430</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:8">
+      <c r="A32">
+        <v>10510</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:8">
+      <c r="A33">
+        <v>10520</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:8">
+      <c r="A34">
+        <v>10530</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:8">
+      <c r="A35">
+        <v>10610</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:8">
+      <c r="A36">
+        <v>10620</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:8">
+      <c r="A37">
+        <v>10630</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:8">
+      <c r="A38">
+        <v>10710</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:8">
+      <c r="A39">
+        <v>10720</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:8">
+      <c r="A40">
+        <v>10730</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:8">
+      <c r="A41">
+        <v>10810</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:8">
+      <c r="A42">
+        <v>10820</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:8">
+      <c r="A43">
+        <v>10830</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:8">
+      <c r="A44">
+        <v>10910</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:8">
+      <c r="A45">
+        <v>10920</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:8">
+      <c r="A46">
+        <v>10930</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:8">
+      <c r="A47">
+        <v>11010</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:8">
+      <c r="A48">
+        <v>11020</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:8">
+      <c r="A49">
+        <v>11030</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
+        <v>20010</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:8">
+      <c r="A51">
+        <v>20020</v>
+      </c>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>30010</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>1010</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:8">
+      <c r="A53">
+        <v>30011</v>
+      </c>
+      <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>30020</v>
+      </c>
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>30030</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>30040</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>30050</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>30060</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>30110</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
         <v>2010</v>
       </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1910,7 +2751,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1918,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1926,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1934,7 +2775,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1942,7 +2783,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1950,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1958,7 +2799,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1966,7 +2807,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1974,7 +2815,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1982,7 +2823,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1990,7 +2831,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1998,7 +2839,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2006,7 +2847,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2014,7 +2855,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2022,7 +2863,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -265,10 +265,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -276,60 +276,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -348,23 +294,29 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -379,8 +331,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -393,18 +353,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -422,6 +415,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -432,13 +432,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,169 +612,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -651,36 +651,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -704,11 +674,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -731,145 +731,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Advs" sheetId="1" r:id="rId1"/>
@@ -265,97 +265,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -377,16 +295,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -394,8 +311,22 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -410,7 +341,38 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -422,6 +384,44 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -432,187 +432,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,11 +626,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,50 +656,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -715,6 +682,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -723,6 +708,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -731,145 +731,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -886,12 +886,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>Id</t>
   </si>
@@ -80,6 +80,9 @@
     <t>Magic</t>
   </si>
   <si>
+    <t>Magic_2</t>
+  </si>
+  <si>
     <t>BeforeBoss</t>
   </si>
   <si>
@@ -183,6 +186,15 @@
   </si>
   <si>
     <t>Actor0010_3</t>
+  </si>
+  <si>
+    <t>Actor0101_1</t>
+  </si>
+  <si>
+    <t>Actor0101_2</t>
+  </si>
+  <si>
+    <t>Actor0101_3</t>
   </si>
   <si>
     <t>Interrude0-1</t>
@@ -274,6 +286,37 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -295,6 +338,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -310,11 +368,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,26 +390,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -370,54 +428,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -432,6 +444,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -444,175 +462,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,6 +635,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -637,6 +664,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -665,39 +725,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -708,21 +735,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -731,7 +743,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,136 +752,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1196,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="7" width="13.2727272727273" customWidth="1"/>
@@ -1569,7 +1581,7 @@
     </row>
     <row r="15" customFormat="1" spans="1:8">
       <c r="A15">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
@@ -1593,9 +1605,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" customFormat="1" spans="1:8">
       <c r="A16">
-        <v>1030</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -1619,9 +1631,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:8">
+    <row r="17" spans="1:8">
       <c r="A17">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
@@ -1647,7 +1659,7 @@
     </row>
     <row r="18" customFormat="1" spans="1:8">
       <c r="A18">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1673,7 +1685,7 @@
     </row>
     <row r="19" customFormat="1" spans="1:8">
       <c r="A19">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
@@ -1697,9 +1709,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" customFormat="1" spans="1:8">
       <c r="A20">
-        <v>10110</v>
+        <v>1060</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
@@ -1723,9 +1735,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:8">
+    <row r="21" spans="1:8">
       <c r="A21">
-        <v>10120</v>
+        <v>10110</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -1751,7 +1763,7 @@
     </row>
     <row r="22" customFormat="1" spans="1:8">
       <c r="A22">
-        <v>10130</v>
+        <v>10120</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
@@ -1777,7 +1789,7 @@
     </row>
     <row r="23" customFormat="1" spans="1:8">
       <c r="A23">
-        <v>10210</v>
+        <v>10130</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
@@ -1803,7 +1815,7 @@
     </row>
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
-        <v>10220</v>
+        <v>10210</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -1829,7 +1841,7 @@
     </row>
     <row r="25" customFormat="1" spans="1:8">
       <c r="A25">
-        <v>10230</v>
+        <v>10220</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1855,7 +1867,7 @@
     </row>
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
-        <v>10310</v>
+        <v>10230</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -1881,7 +1893,7 @@
     </row>
     <row r="27" customFormat="1" spans="1:8">
       <c r="A27">
-        <v>10320</v>
+        <v>10310</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -1907,7 +1919,7 @@
     </row>
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
-        <v>10330</v>
+        <v>10320</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -1933,7 +1945,7 @@
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>10410</v>
+        <v>10330</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -1959,7 +1971,7 @@
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
-        <v>10420</v>
+        <v>10410</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
@@ -1985,7 +1997,7 @@
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
-        <v>10430</v>
+        <v>10420</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -2011,7 +2023,7 @@
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
-        <v>10510</v>
+        <v>10430</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
@@ -2037,7 +2049,7 @@
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
-        <v>10520</v>
+        <v>10510</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
@@ -2063,7 +2075,7 @@
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
-        <v>10530</v>
+        <v>10520</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
@@ -2089,7 +2101,7 @@
     </row>
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
-        <v>10610</v>
+        <v>10530</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -2115,7 +2127,7 @@
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
-        <v>10620</v>
+        <v>10610</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
@@ -2141,7 +2153,7 @@
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
-        <v>10630</v>
+        <v>10620</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2167,7 +2179,7 @@
     </row>
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
-        <v>10710</v>
+        <v>10630</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
@@ -2193,7 +2205,7 @@
     </row>
     <row r="39" customFormat="1" spans="1:8">
       <c r="A39">
-        <v>10720</v>
+        <v>10710</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
@@ -2219,7 +2231,7 @@
     </row>
     <row r="40" customFormat="1" spans="1:8">
       <c r="A40">
-        <v>10730</v>
+        <v>10720</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -2245,7 +2257,7 @@
     </row>
     <row r="41" customFormat="1" spans="1:8">
       <c r="A41">
-        <v>10810</v>
+        <v>10730</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -2271,7 +2283,7 @@
     </row>
     <row r="42" customFormat="1" spans="1:8">
       <c r="A42">
-        <v>10820</v>
+        <v>10810</v>
       </c>
       <c r="B42" t="s">
         <v>48</v>
@@ -2297,7 +2309,7 @@
     </row>
     <row r="43" customFormat="1" spans="1:8">
       <c r="A43">
-        <v>10830</v>
+        <v>10820</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -2323,7 +2335,7 @@
     </row>
     <row r="44" customFormat="1" spans="1:8">
       <c r="A44">
-        <v>10910</v>
+        <v>10830</v>
       </c>
       <c r="B44" t="s">
         <v>50</v>
@@ -2349,7 +2361,7 @@
     </row>
     <row r="45" customFormat="1" spans="1:8">
       <c r="A45">
-        <v>10920</v>
+        <v>10910</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -2375,7 +2387,7 @@
     </row>
     <row r="46" customFormat="1" spans="1:8">
       <c r="A46">
-        <v>10930</v>
+        <v>10920</v>
       </c>
       <c r="B46" t="s">
         <v>52</v>
@@ -2401,7 +2413,7 @@
     </row>
     <row r="47" customFormat="1" spans="1:8">
       <c r="A47">
-        <v>11010</v>
+        <v>10930</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
@@ -2427,7 +2439,7 @@
     </row>
     <row r="48" customFormat="1" spans="1:8">
       <c r="A48">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -2453,7 +2465,7 @@
     </row>
     <row r="49" customFormat="1" spans="1:8">
       <c r="A49">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -2477,9 +2489,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" customFormat="1" spans="1:8">
       <c r="A50">
-        <v>20010</v>
+        <v>11030</v>
       </c>
       <c r="B50" t="s">
         <v>56</v>
@@ -2505,7 +2517,7 @@
     </row>
     <row r="51" customFormat="1" spans="1:8">
       <c r="A51">
-        <v>20020</v>
+        <v>12010</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
@@ -2529,9 +2541,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" customFormat="1" spans="1:8">
       <c r="A52">
-        <v>30010</v>
+        <v>12020</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -2540,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2557,7 +2569,7 @@
     </row>
     <row r="53" customFormat="1" spans="1:8">
       <c r="A53">
-        <v>30011</v>
+        <v>12030</v>
       </c>
       <c r="B53" t="s">
         <v>59</v>
@@ -2583,7 +2595,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>30020</v>
+        <v>20010</v>
       </c>
       <c r="B54" t="s">
         <v>60</v>
@@ -2607,9 +2619,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" customFormat="1" spans="1:8">
       <c r="A55">
-        <v>30030</v>
+        <v>20020</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
@@ -2635,7 +2647,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>30040</v>
+        <v>30010</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
@@ -2644,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2659,9 +2671,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" customFormat="1" spans="1:8">
       <c r="A57">
-        <v>30050</v>
+        <v>30011</v>
       </c>
       <c r="B57" t="s">
         <v>63</v>
@@ -2687,7 +2699,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>30060</v>
+        <v>30020</v>
       </c>
       <c r="B58" t="s">
         <v>64</v>
@@ -2713,7 +2725,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>30110</v>
+        <v>30030</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
@@ -2722,18 +2734,122 @@
         <v>0</v>
       </c>
       <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>30040</v>
+      </c>
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>30050</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>30060</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>30110</v>
+      </c>
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
         <v>2010</v>
       </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59" t="b">
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2751,7 +2867,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2759,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2767,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2775,7 +2891,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2783,7 +2899,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2791,7 +2907,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2799,7 +2915,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2807,7 +2923,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2815,7 +2931,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2823,7 +2939,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2831,7 +2947,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2839,7 +2955,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2847,7 +2963,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2855,7 +2971,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2863,7 +2979,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Id</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>BeforeBoss</t>
+  </si>
+  <si>
+    <t>RotateCamera</t>
   </si>
   <si>
     <t>Dungeon30-1</t>
@@ -291,9 +294,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,9 +377,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,31 +393,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -368,23 +407,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -398,36 +431,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -444,13 +447,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,13 +519,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -480,13 +579,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,73 +603,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -576,49 +621,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,21 +638,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -664,6 +652,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -701,26 +704,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -743,7 +746,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -752,136 +755,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1208,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="7" width="13.2727272727273" customWidth="1"/>
@@ -1631,9 +1634,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" customFormat="1" spans="1:8">
       <c r="A17">
-        <v>1030</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
@@ -1657,9 +1660,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:8">
+    <row r="18" spans="1:8">
       <c r="A18">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1685,7 +1688,7 @@
     </row>
     <row r="19" customFormat="1" spans="1:8">
       <c r="A19">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
@@ -1711,7 +1714,7 @@
     </row>
     <row r="20" customFormat="1" spans="1:8">
       <c r="A20">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
@@ -1735,9 +1738,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" customFormat="1" spans="1:8">
       <c r="A21">
-        <v>10110</v>
+        <v>1060</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -1761,9 +1764,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:8">
+    <row r="22" spans="1:8">
       <c r="A22">
-        <v>10120</v>
+        <v>10110</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
@@ -1789,7 +1792,7 @@
     </row>
     <row r="23" customFormat="1" spans="1:8">
       <c r="A23">
-        <v>10130</v>
+        <v>10120</v>
       </c>
       <c r="B23" t="s">
         <v>29</v>
@@ -1815,7 +1818,7 @@
     </row>
     <row r="24" customFormat="1" spans="1:8">
       <c r="A24">
-        <v>10210</v>
+        <v>10130</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
@@ -1841,7 +1844,7 @@
     </row>
     <row r="25" customFormat="1" spans="1:8">
       <c r="A25">
-        <v>10220</v>
+        <v>10210</v>
       </c>
       <c r="B25" t="s">
         <v>31</v>
@@ -1867,7 +1870,7 @@
     </row>
     <row r="26" customFormat="1" spans="1:8">
       <c r="A26">
-        <v>10230</v>
+        <v>10220</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -1893,7 +1896,7 @@
     </row>
     <row r="27" customFormat="1" spans="1:8">
       <c r="A27">
-        <v>10310</v>
+        <v>10230</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -1919,7 +1922,7 @@
     </row>
     <row r="28" customFormat="1" spans="1:8">
       <c r="A28">
-        <v>10320</v>
+        <v>10310</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -1945,7 +1948,7 @@
     </row>
     <row r="29" customFormat="1" spans="1:8">
       <c r="A29">
-        <v>10330</v>
+        <v>10320</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -1971,7 +1974,7 @@
     </row>
     <row r="30" customFormat="1" spans="1:8">
       <c r="A30">
-        <v>10410</v>
+        <v>10330</v>
       </c>
       <c r="B30" t="s">
         <v>36</v>
@@ -1997,7 +2000,7 @@
     </row>
     <row r="31" customFormat="1" spans="1:8">
       <c r="A31">
-        <v>10420</v>
+        <v>10410</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -2023,7 +2026,7 @@
     </row>
     <row r="32" customFormat="1" spans="1:8">
       <c r="A32">
-        <v>10430</v>
+        <v>10420</v>
       </c>
       <c r="B32" t="s">
         <v>38</v>
@@ -2049,7 +2052,7 @@
     </row>
     <row r="33" customFormat="1" spans="1:8">
       <c r="A33">
-        <v>10510</v>
+        <v>10430</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
@@ -2075,7 +2078,7 @@
     </row>
     <row r="34" customFormat="1" spans="1:8">
       <c r="A34">
-        <v>10520</v>
+        <v>10510</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
@@ -2101,7 +2104,7 @@
     </row>
     <row r="35" customFormat="1" spans="1:8">
       <c r="A35">
-        <v>10530</v>
+        <v>10520</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -2127,7 +2130,7 @@
     </row>
     <row r="36" customFormat="1" spans="1:8">
       <c r="A36">
-        <v>10610</v>
+        <v>10530</v>
       </c>
       <c r="B36" t="s">
         <v>42</v>
@@ -2153,7 +2156,7 @@
     </row>
     <row r="37" customFormat="1" spans="1:8">
       <c r="A37">
-        <v>10620</v>
+        <v>10610</v>
       </c>
       <c r="B37" t="s">
         <v>43</v>
@@ -2179,7 +2182,7 @@
     </row>
     <row r="38" customFormat="1" spans="1:8">
       <c r="A38">
-        <v>10630</v>
+        <v>10620</v>
       </c>
       <c r="B38" t="s">
         <v>44</v>
@@ -2205,7 +2208,7 @@
     </row>
     <row r="39" customFormat="1" spans="1:8">
       <c r="A39">
-        <v>10710</v>
+        <v>10630</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
@@ -2231,7 +2234,7 @@
     </row>
     <row r="40" customFormat="1" spans="1:8">
       <c r="A40">
-        <v>10720</v>
+        <v>10710</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -2257,7 +2260,7 @@
     </row>
     <row r="41" customFormat="1" spans="1:8">
       <c r="A41">
-        <v>10730</v>
+        <v>10720</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -2283,7 +2286,7 @@
     </row>
     <row r="42" customFormat="1" spans="1:8">
       <c r="A42">
-        <v>10810</v>
+        <v>10730</v>
       </c>
       <c r="B42" t="s">
         <v>48</v>
@@ -2309,7 +2312,7 @@
     </row>
     <row r="43" customFormat="1" spans="1:8">
       <c r="A43">
-        <v>10820</v>
+        <v>10810</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
@@ -2335,7 +2338,7 @@
     </row>
     <row r="44" customFormat="1" spans="1:8">
       <c r="A44">
-        <v>10830</v>
+        <v>10820</v>
       </c>
       <c r="B44" t="s">
         <v>50</v>
@@ -2361,7 +2364,7 @@
     </row>
     <row r="45" customFormat="1" spans="1:8">
       <c r="A45">
-        <v>10910</v>
+        <v>10830</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -2387,7 +2390,7 @@
     </row>
     <row r="46" customFormat="1" spans="1:8">
       <c r="A46">
-        <v>10920</v>
+        <v>10910</v>
       </c>
       <c r="B46" t="s">
         <v>52</v>
@@ -2413,7 +2416,7 @@
     </row>
     <row r="47" customFormat="1" spans="1:8">
       <c r="A47">
-        <v>10930</v>
+        <v>10920</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
@@ -2439,7 +2442,7 @@
     </row>
     <row r="48" customFormat="1" spans="1:8">
       <c r="A48">
-        <v>11010</v>
+        <v>10930</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -2465,7 +2468,7 @@
     </row>
     <row r="49" customFormat="1" spans="1:8">
       <c r="A49">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -2491,7 +2494,7 @@
     </row>
     <row r="50" customFormat="1" spans="1:8">
       <c r="A50">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B50" t="s">
         <v>56</v>
@@ -2517,7 +2520,7 @@
     </row>
     <row r="51" customFormat="1" spans="1:8">
       <c r="A51">
-        <v>12010</v>
+        <v>11030</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
@@ -2543,7 +2546,7 @@
     </row>
     <row r="52" customFormat="1" spans="1:8">
       <c r="A52">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -2569,7 +2572,7 @@
     </row>
     <row r="53" customFormat="1" spans="1:8">
       <c r="A53">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="B53" t="s">
         <v>59</v>
@@ -2593,9 +2596,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" customFormat="1" spans="1:8">
       <c r="A54">
-        <v>20010</v>
+        <v>12030</v>
       </c>
       <c r="B54" t="s">
         <v>60</v>
@@ -2619,9 +2622,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:8">
+    <row r="55" spans="1:8">
       <c r="A55">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
@@ -2645,9 +2648,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" customFormat="1" spans="1:8">
       <c r="A56">
-        <v>30010</v>
+        <v>20020</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
@@ -2656,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2671,9 +2674,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customFormat="1" spans="1:8">
+    <row r="57" spans="1:8">
       <c r="A57">
-        <v>30011</v>
+        <v>30010</v>
       </c>
       <c r="B57" t="s">
         <v>63</v>
@@ -2682,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2697,9 +2700,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" customFormat="1" spans="1:8">
       <c r="A58">
-        <v>30020</v>
+        <v>30011</v>
       </c>
       <c r="B58" t="s">
         <v>64</v>
@@ -2725,7 +2728,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
@@ -2751,7 +2754,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B60" t="s">
         <v>66</v>
@@ -2777,7 +2780,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>30050</v>
+        <v>30040</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
@@ -2803,7 +2806,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>30060</v>
+        <v>30050</v>
       </c>
       <c r="B62" t="s">
         <v>68</v>
@@ -2829,7 +2832,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>30110</v>
+        <v>30060</v>
       </c>
       <c r="B63" t="s">
         <v>69</v>
@@ -2838,18 +2841,44 @@
         <v>0</v>
       </c>
       <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>30110</v>
+      </c>
+      <c r="B64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
         <v>2010</v>
       </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63" t="b">
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2867,7 +2896,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2875,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2883,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2891,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2899,7 +2928,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2907,7 +2936,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2915,7 +2944,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2923,7 +2952,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2931,7 +2960,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2939,7 +2968,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2947,7 +2976,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2955,7 +2984,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2963,7 +2992,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2971,7 +3000,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2979,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
